--- a/results/result_1.xlsx
+++ b/results/result_1.xlsx
@@ -463,12 +463,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>第七届全国青少年人工智能创新挑战赛</t>
+          <t>三维程序创意设计专项赛</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>三维程序创意设计专项赛</t>
+          <t>第七届全国青少年人工智能创新挑战赛</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -476,23 +476,31 @@
           <t>2024年4月</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr"/>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>2024 年4 月15 日-5 月15 日</t>
+        </is>
+      </c>
       <c r="E2" t="inlineStr">
         <is>
           <t>中国少年儿童发展服务中心</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr"/>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>https://aiic.china61.org.cn/</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>第七届全国青少年人工智能创新挑战赛</t>
+          <t>太空电梯工程设计专项赛</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>太空电梯工程设计专项赛</t>
+          <t>第七届全国青少年人工智能创新挑战赛</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -506,17 +514,21 @@
           <t>中国少年儿童发展服务中心</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr"/>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>http://www.china61.org.cn</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>第七届全国青少年人工智能创新挑战赛</t>
+          <t>开源鸿蒙机器人专项赛</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>开源鸿蒙机器人专项赛</t>
+          <t>第七届全国青少年人工智能创新挑战赛</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -524,47 +536,59 @@
           <t>2024年4月</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr"/>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>2024 年4 月15 日-5 月15 日</t>
+        </is>
+      </c>
       <c r="E4" t="inlineStr">
         <is>
           <t>中国少年儿童发展服务中心</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr"/>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>https://aiic.china61.org.cn/</t>
+        </is>
+      </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr">
+      <c r="A5" t="inlineStr"/>
+      <c r="B5" t="inlineStr">
         <is>
           <t>泰迪杯数据挖掘挑战赛组织委员会</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>2024年3月</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>2024 年3 月8 日-4 月12 日</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
         <is>
           <t>泰迪杯组委会 (2024)】 1号</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>2024年3月</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr"/>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>泰迪杯组委会 (2024)】 1号</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr"/>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>https://www.tipdm.org:10010</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>第七届全国青少年人工智能创新挑战赛</t>
+          <t>无人驾驶智能车专项赛</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>无人驾驶智能车专项赛</t>
+          <t>第七届全国青少年人工智能创新挑战赛</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -572,23 +596,31 @@
           <t>2024年4月</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr"/>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>2024 年4 月15 日-5 月15 日</t>
+        </is>
+      </c>
       <c r="E6" t="inlineStr">
         <is>
           <t>中国少年儿童发展服务中心</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr"/>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>http://aiic.china61.org.cn/</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>第七届全国青少年人工智能创新挑战赛</t>
+          <t>3D 编程模型创新设计专项赛</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>3D 编程模型创新设计专项赛</t>
+          <t>第七届全国青少年人工智能创新挑战赛</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -596,23 +628,31 @@
           <t>2024年4月</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr"/>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>2024年4月15日-5月15日</t>
+        </is>
+      </c>
       <c r="E7" t="inlineStr">
         <is>
           <t>中国少年儿童发展服务中心</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr"/>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>https://aiic.china61.org.cn/</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>第七届全国青少年人工智能创新挑战赛</t>
+          <t>机器人工程设计专项赛</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>机器人工程设计专项赛</t>
+          <t>第七届全国青少年人工智能创新挑战赛</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -620,23 +660,31 @@
           <t>2024年4月</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr"/>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>2024 年4 月15 日- 5 月15 日</t>
+        </is>
+      </c>
       <c r="E8" t="inlineStr">
         <is>
           <t>中国少年儿童发展服务中心</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr"/>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>https://aiic.china61.org.cn/</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>第七届全国青少年人工智能创新挑战赛</t>
+          <t>虚拟仿真平台创新设计专项赛</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>虚拟仿真平台创新设计专项赛</t>
+          <t>第七届全国青少年人工智能创新挑战赛</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -644,23 +692,31 @@
           <t>2024年4月</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr"/>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>2024 年4 月15 日-5 月15 日</t>
+        </is>
+      </c>
       <c r="E9" t="inlineStr">
         <is>
           <t>中国少年儿童发展服务中心</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr"/>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>https://aiic.china61.org.cn/</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>第七届全国青少年人工智能创新挑战赛</t>
+          <t>觉技机器人专项赛</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>觉技机器人专项赛</t>
+          <t>第七届全国青少年人工智能创新挑战赛</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -668,23 +724,31 @@
           <t>2024年4月</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr"/>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>2024 年4 月15 日-5 月15 日</t>
+        </is>
+      </c>
       <c r="E10" t="inlineStr">
         <is>
           <t>中国少年儿童发展服务中心</t>
         </is>
       </c>
-      <c r="F10" t="inlineStr"/>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>https://aiic.china61.org.cn/</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>第七届全国青少年人工智能创新挑战赛</t>
+          <t>智能必片与计算思维专项赛</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>智能必片与计算思维专项赛</t>
+          <t>第七届全国青少年人工智能创新挑战赛</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -692,23 +756,31 @@
           <t>2024年4月</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr"/>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>2024年4月15日-5月15日</t>
+        </is>
+      </c>
       <c r="E11" t="inlineStr">
         <is>
           <t>中国少年儿童发展服务中心</t>
         </is>
       </c>
-      <c r="F11" t="inlineStr"/>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>https://aiic.china61.org.cn/</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>第七届全国青少年人工智能创新挑战赛</t>
+          <t>人工智能综合创新专项赛</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>人工智能综合创新专项赛</t>
+          <t>第七届全国青少年人工智能创新挑战赛</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -716,23 +788,31 @@
           <t>2024年4月</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr"/>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>2024年4月15日-5月15日</t>
+        </is>
+      </c>
       <c r="E12" t="inlineStr">
         <is>
           <t>中国少年儿童发展服务中心</t>
         </is>
       </c>
-      <c r="F12" t="inlineStr"/>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>https://aiic.china61.org.cn/</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>第七届全国青少年人工智能创新挑战赛</t>
+          <t>“未来校园”智能应用专项赛</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>“未来校园”智能应用专项赛</t>
+          <t>第七届全国青少年人工智能创新挑战赛</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -740,23 +820,31 @@
           <t>2024年4月</t>
         </is>
       </c>
-      <c r="D13" t="inlineStr"/>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>2024年4月15日-5月15日</t>
+        </is>
+      </c>
       <c r="E13" t="inlineStr">
         <is>
           <t>中国少年儿童发展服务中心</t>
         </is>
       </c>
-      <c r="F13" t="inlineStr"/>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>https://aiic.china61.org.cn/</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>第七届全国青少年人工智能创新挑战赛</t>
+          <t>智慧城市主题设计专项赛</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>智慧城市主题设计专项赛</t>
+          <t>第七届全国青少年人工智能创新挑战赛</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -764,23 +852,31 @@
           <t>2024年4月</t>
         </is>
       </c>
-      <c r="D14" t="inlineStr"/>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>2024 年4 月15 日- 5 月15 日</t>
+        </is>
+      </c>
       <c r="E14" t="inlineStr">
         <is>
           <t>中国少年儿童发展服务中心</t>
         </is>
       </c>
-      <c r="F14" t="inlineStr"/>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>https://aiic.china61.org.cn/</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>第七届全国青少年人工智能创新挑战赛</t>
+          <t>智能数据采集装置设计专项赛</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>智能数据采集装置设计专项赛</t>
+          <t>第七届全国青少年人工智能创新挑战赛</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -788,23 +884,31 @@
           <t>2024年4月</t>
         </is>
       </c>
-      <c r="D15" t="inlineStr"/>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>2024 年4 月15 日-5 月15 日</t>
+        </is>
+      </c>
       <c r="E15" t="inlineStr">
         <is>
           <t>中国少年儿童发展服务中心</t>
         </is>
       </c>
-      <c r="F15" t="inlineStr"/>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>https://aiic.china61.org.cn/</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>第七届全国青少年人工智能创新挑战赛</t>
+          <t>太空探索智能机器人专项赛</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>太空探索智能机器人专项赛</t>
+          <t>第七届全国青少年人工智能创新挑战赛</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -812,23 +916,31 @@
           <t>2024年4月</t>
         </is>
       </c>
-      <c r="D16" t="inlineStr"/>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>2024 年4 月15 日-5 月15 日</t>
+        </is>
+      </c>
       <c r="E16" t="inlineStr">
         <is>
           <t>中国少年儿童发展服务中心</t>
         </is>
       </c>
-      <c r="F16" t="inlineStr"/>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>https://aiic.china61.org.cn/</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>第七届全国青少年人工智能创新挑战赛</t>
+          <t>极地资源勘探专项赛</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>极地资源勘探专项赛</t>
+          <t>第七届全国青少年人工智能创新挑战赛</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -842,17 +954,21 @@
           <t>中国少年儿童发展服务中心</t>
         </is>
       </c>
-      <c r="F17" t="inlineStr"/>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>http://www.china61.org.cn</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>第七届全国青少年人工智能创新挑战赛</t>
+          <t>生成式人工智能应用专项赛</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>生成式人工智能应用专项赛</t>
+          <t>第七届全国青少年人工智能创新挑战赛</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -860,23 +976,31 @@
           <t>2024年4月</t>
         </is>
       </c>
-      <c r="D18" t="inlineStr"/>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>2024 年4 月15 日-5 月15 日</t>
+        </is>
+      </c>
       <c r="E18" t="inlineStr">
         <is>
           <t>中国少年儿童发展服务中心</t>
         </is>
       </c>
-      <c r="F18" t="inlineStr"/>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>http://www.china61.org.cn</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>第七届全国青少年人工智能创新挑战赛</t>
+          <t>编程创作与信息学专项赛</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>编程创作与信息学专项赛</t>
+          <t>第七届全国青少年人工智能创新挑战赛</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -884,13 +1008,21 @@
           <t>2024年4月</t>
         </is>
       </c>
-      <c r="D19" t="inlineStr"/>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>2024年4月15日-5月15日</t>
+        </is>
+      </c>
       <c r="E19" t="inlineStr">
         <is>
           <t>中国少年儿童发展服务中心</t>
         </is>
       </c>
-      <c r="F19" t="inlineStr"/>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>https://aiic.china61.org.cn/</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
